--- a/4.质量管理/2.运行记录类文件/TXHS-04-21-2026年1-3月运维服务能力指标完成情况 .xlsx
+++ b/4.质量管理/2.运行记录类文件/TXHS-04-21-2026年1-3月运维服务能力指标完成情况 .xlsx
@@ -308,16 +308,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color indexed="8"/>
-      <name val="楷体_GB2312"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
+      <b/>
+      <sz val="10"/>
       <color indexed="8"/>
-      <name val="宋体"/>
+      <name val="楷体_GB2312"/>
       <charset val="134"/>
     </font>
     <font>
@@ -885,50 +885,56 @@
     <xf numFmtId="43" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="22" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="1" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="2" fillId="3" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1330,7 +1336,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.75" style="2" customWidth="1"/>
@@ -1342,7 +1348,7 @@
     <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.75" customHeight="1" spans="1:9">
+    <row r="1" ht="13" customHeight="1" spans="1:9">
       <c r="A1" s="3"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -1367,8 +1373,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="7">
-        <f>ROW()-2</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>3</v>
@@ -1383,20 +1388,19 @@
       <c r="F2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="7">
-        <f t="shared" ref="A3:A12" si="0">ROW()-2</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -1409,20 +1413,19 @@
       <c r="F3" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="1" t="s">
+      <c r="G3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -1435,20 +1438,19 @@
       <c r="F4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="G4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -1461,20 +1463,19 @@
       <c r="F5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I5" s="1" t="s">
+      <c r="G5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>14</v>
@@ -1491,20 +1492,19 @@
       <c r="F6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="10">
+      <c r="G6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="7">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
@@ -1519,20 +1519,19 @@
       <c r="F7" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I7" s="10">
+      <c r="G7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="7">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
@@ -1547,20 +1546,19 @@
       <c r="F8" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="10">
+      <c r="G8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="7">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8" t="s">
@@ -1575,20 +1573,19 @@
       <c r="F9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="10">
+      <c r="G9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I9" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="7">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8" t="s">
@@ -1603,20 +1600,19 @@
       <c r="F10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="10">
+      <c r="G10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="7">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8" t="s">
@@ -1631,20 +1627,19 @@
       <c r="F11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" s="10" t="s">
+      <c r="G11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="7">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>30</v>
@@ -1661,20 +1656,19 @@
       <c r="F12" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="10" t="s">
+      <c r="G12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I12" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="7">
-        <f t="shared" ref="A13:A22" si="1">ROW()-2</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8" t="s">
@@ -1689,20 +1683,19 @@
       <c r="F13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="10">
+      <c r="G13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="7">
-        <f t="shared" si="1"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
@@ -1717,20 +1710,19 @@
       <c r="F14" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" s="10">
+      <c r="G14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="7">
-        <f t="shared" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8" t="s">
@@ -1745,20 +1737,19 @@
       <c r="F15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="10">
-        <v>1</v>
-      </c>
-      <c r="H15" s="10">
-        <v>1</v>
-      </c>
-      <c r="I15" s="10">
+      <c r="G15" s="11">
+        <v>1</v>
+      </c>
+      <c r="H15" s="11">
+        <v>1</v>
+      </c>
+      <c r="I15" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="7">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -1771,20 +1762,19 @@
       <c r="F16" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="10">
+      <c r="G16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I16" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="7">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8" t="s">
@@ -1799,20 +1789,19 @@
       <c r="F17" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17" s="10">
+      <c r="G17" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I17" s="11">
         <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="7">
-        <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -1825,20 +1814,19 @@
       <c r="F18" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="10">
+      <c r="G18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I18" s="11">
         <v>0.92</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="7">
-        <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8" t="s">
@@ -1853,20 +1841,19 @@
       <c r="F19" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="10" t="s">
+      <c r="G19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="7">
-        <f t="shared" si="1"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8" t="s">
@@ -1881,20 +1868,19 @@
       <c r="F20" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="10">
-        <v>1</v>
-      </c>
-      <c r="H20" s="10">
-        <v>1</v>
-      </c>
-      <c r="I20" s="10">
+      <c r="G20" s="11">
+        <v>1</v>
+      </c>
+      <c r="H20" s="11">
+        <v>1</v>
+      </c>
+      <c r="I20" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="7">
-        <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8" t="s">
@@ -1909,20 +1895,19 @@
       <c r="F21" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="10">
-        <v>1</v>
-      </c>
-      <c r="H21" s="10">
-        <v>1</v>
-      </c>
-      <c r="I21" s="10">
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="H21" s="11">
+        <v>1</v>
+      </c>
+      <c r="I21" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="7">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
@@ -1937,20 +1922,19 @@
       <c r="F22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="10">
-        <v>1</v>
-      </c>
-      <c r="H22" s="10">
-        <v>1</v>
-      </c>
-      <c r="I22" s="10">
+      <c r="G22" s="11">
+        <v>1</v>
+      </c>
+      <c r="H22" s="11">
+        <v>1</v>
+      </c>
+      <c r="I22" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="7">
-        <f t="shared" ref="A23:A34" si="2">ROW()-2</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
@@ -1963,20 +1947,19 @@
       <c r="F23" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="7">
-        <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8" t="s">
@@ -1991,20 +1974,19 @@
       <c r="F24" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" s="10" t="s">
+      <c r="G24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="7">
-        <f t="shared" si="2"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
@@ -2019,20 +2001,19 @@
       <c r="F25" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I25" s="10" t="s">
+      <c r="G25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="7">
-        <f t="shared" si="2"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>61</v>
@@ -2047,20 +2028,19 @@
       <c r="F26" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I26" s="10">
+      <c r="G26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="7">
-        <f t="shared" si="2"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -2073,20 +2053,19 @@
       <c r="F27" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="G27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="7">
-        <f t="shared" si="2"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>65</v>
@@ -2103,20 +2082,19 @@
       <c r="F28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I28" s="10">
+      <c r="G28" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="7">
-        <f t="shared" si="2"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8" t="s">
@@ -2131,20 +2109,22 @@
       <c r="F29" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I29" s="10">
+      <c r="G29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="11">
         <v>0.9</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="7"/>
+      <c r="A30" s="7">
+        <v>29</v>
+      </c>
       <c r="B30" s="8"/>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="13" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="9" t="s">
@@ -2159,17 +2139,19 @@
       <c r="G30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="H30" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="7"/>
+      <c r="A31" s="7">
+        <v>30</v>
+      </c>
       <c r="B31" s="8"/>
-      <c r="C31" s="12"/>
+      <c r="C31" s="14"/>
       <c r="D31" s="9" t="s">
         <v>72</v>
       </c>
@@ -2179,20 +2161,19 @@
       <c r="F31" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I31" s="10">
+      <c r="G31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="7">
-        <f>ROW()-2</f>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8" t="s">
@@ -2207,20 +2188,19 @@
       <c r="F32" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I32" s="13" t="s">
+      <c r="G32" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" s="15" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1" spans="1:9">
       <c r="A33" s="7">
-        <f>ROW()-2</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="8" t="s">
@@ -2235,20 +2215,19 @@
       <c r="F33" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="G33" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="7">
-        <f>ROW()-2</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="8"/>
       <c r="C34" s="8" t="s">
@@ -2263,20 +2242,19 @@
       <c r="F34" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I34" s="1" t="s">
+      <c r="G34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" s="10" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="7">
-        <f>ROW()-2</f>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>82</v>
@@ -2285,26 +2263,25 @@
       <c r="D35" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="16">
         <v>1</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="G35" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" s="10" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="7">
-        <f>ROW()-2</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>84</v>
@@ -2319,13 +2296,13 @@
       <c r="F36" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I36" s="1" t="s">
+      <c r="G36" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" s="10" t="s">
         <v>7</v>
       </c>
     </row>
